--- a/instagram-daily-checker/reports/2026-08-30.xlsx
+++ b/instagram-daily-checker/reports/2026-08-30.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>取得日時：2026-08-30 05:53:30</t>
+          <t>取得日時：2026-08-30 06:22:27</t>
         </is>
       </c>
     </row>

--- a/instagram-daily-checker/reports/2026-08-30.xlsx
+++ b/instagram-daily-checker/reports/2026-08-30.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>取得日時：2026-08-30 06:22:27</t>
+          <t>取得日時：2026-08-30 06:43:08</t>
         </is>
       </c>
     </row>
